--- a/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
+++ b/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BBNPPTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\BBNPPTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66582C1F-0C47-42E5-9226-B6D9CE2514BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED5C7C3-C6DD-4CC0-A75D-D5DA17DC76DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="38865" windowHeight="17235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Source:</t>
   </si>
@@ -134,10 +134,13 @@
     <t>This is a Boolean value that should be set to 0 or 1 in each year.</t>
   </si>
   <si>
-    <t>2028 and new combined cycle gas without CCS is banned starting in 2032.</t>
-  </si>
-  <si>
     <t>In the U.S., we use this to represent EPA 111 Rules. New coal without CCS is banned starting in</t>
+  </si>
+  <si>
+    <t>We also assume no new coal with CCS can be built prior to 2028 given the state of the technology</t>
+  </si>
+  <si>
+    <t>and the construction time for new or modified plants.</t>
   </si>
 </sst>
 </file>
@@ -520,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="60.85546875" customWidth="1"/>
@@ -571,12 +574,22 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>33</v>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -696,14 +709,14 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" s="5">
         <v>0</v>
@@ -791,14 +804,14 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -886,14 +899,14 @@
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -920,75 +933,75 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
@@ -1076,14 +1089,14 @@
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -1171,14 +1184,14 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" s="5">
         <v>0</v>
@@ -1266,14 +1279,14 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -1361,14 +1374,14 @@
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
@@ -1456,14 +1469,14 @@
       <c r="A10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
       </c>
       <c r="E10" s="5">
         <v>0</v>
@@ -1551,14 +1564,14 @@
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
@@ -1646,14 +1659,14 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
       </c>
       <c r="E12" s="5">
         <v>0</v>
@@ -1741,14 +1754,14 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0</v>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
       </c>
       <c r="E13" s="5">
         <v>0</v>
@@ -1836,14 +1849,14 @@
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="5">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0</v>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
       <c r="E14" s="5">
         <v>0</v>
@@ -1931,14 +1944,14 @@
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0</v>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
       </c>
       <c r="E15" s="5">
         <v>0</v>
@@ -2026,14 +2039,14 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0</v>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
       </c>
       <c r="E16" s="5">
         <v>0</v>
@@ -2121,14 +2134,14 @@
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0</v>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
       </c>
       <c r="E17" s="5">
         <v>0</v>
@@ -2216,14 +2229,14 @@
       <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="5">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0</v>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
       </c>
       <c r="E18" s="5">
         <v>0</v>
@@ -2311,26 +2324,26 @@
       <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="5">
-        <v>0</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0</v>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
       </c>
       <c r="E19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -2406,26 +2419,26 @@
       <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="5">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0</v>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
       </c>
       <c r="E20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -2501,26 +2514,26 @@
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="5">
-        <v>0</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0</v>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
@@ -2596,26 +2609,26 @@
       <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="5">
-        <v>0</v>
-      </c>
-      <c r="C22" s="5">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0</v>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
       </c>
       <c r="E22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
@@ -2691,14 +2704,14 @@
       <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="5">
-        <v>0</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0</v>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
       </c>
       <c r="E23" s="5">
         <v>0</v>
@@ -2786,14 +2799,14 @@
       <c r="A24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="5">
-        <v>0</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0</v>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
       </c>
       <c r="E24" s="5">
         <v>0</v>
@@ -2881,14 +2894,14 @@
       <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="5">
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0</v>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
       </c>
       <c r="E25" s="5">
         <v>0</v>
